--- a/scripts/DoAn4_Bemori/AI/TestCase/TC/Excel/Sample_TestCase_Bemori.xlsx
+++ b/scripts/DoAn4_Bemori/AI/TestCase/TC/Excel/Sample_TestCase_Bemori.xlsx
@@ -715,31 +715,27 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Kiểm thử chức năng tìm kiếm khi nhập từ khóa hợp lệ.</t>
+          <t>Kiểm tra chức năng tìm kiếm sản phẩm với từ khóa hợp lệ</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị trang cửa hàng.</t>
+          <t>Người dùng đang ở trang chủ website</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Người dùng nhập từ khóa tìm kiếm vào ô tìm kiếm.
-Step 2: Người dùng nhấn nút "Tìm kiếm".
-Step 3: Kiểm tra danh sách sản phẩm phù hợp với từ khóa đã hiển thị.</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>Hệ thống hiển thị danh sách các sản phẩm khớp với từ khóa tìm kiếm.</t>
-        </is>
-      </c>
+          <t>Step 1: Nhập từ khóa tìm kiếm vào ô tìm kiếm
+Step 2: Nhấn nút "Tìm kiếm"
+Step 3: Kiểm tra danh sách sản phẩm phù hợp hiển thị</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="I5" s="11" t="n"/>
@@ -752,36 +748,32 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Kiểm thử chức năng tìm kiếm khi người dùng không nhập từ khóa.</t>
+          <t>Kiểm tra chức năng tìm kiếm khi không nhập từ khóa (không có lỗi)</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị trang cửa hàng.</t>
+          <t>Người dùng đang ở trang chủ website</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Người dùng không nhập bất kỳ ký tự nào vào ô tìm kiếm.
-Step 2: Người dùng nhấn nút "Tìm kiếm".
-Step 3: Kiểm tra danh sách toàn bộ sản phẩm trong cửa hàng được hiển thị.</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>Hệ thống hiển thị toàn bộ danh sách sản phẩm có sẵn trong cửa hàng.</t>
-        </is>
-      </c>
+          <t>Step 1: Không nhập từ khóa
+Step 2: Nhấn nút "Tìm kiếm"
+Step 3: Kiểm tra hiển thị tất cả danh sách sản phẩm trong cửa hàng</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr"/>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="I6" s="11" t="n"/>
     </row>
-    <row r="7" ht="45" customHeight="1">
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>TC_003</t>
@@ -789,31 +781,32 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Kiểm thử chức năng tìm kiếm khi không có sản phẩm phù hợp.</t>
+          <t>Kiểm tra chức năng tìm kiếm khi không có kết quả phù hợp</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị trang cửa hàng.</t>
+          <t>Người dùng đang ở trang chủ website</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Người dùng nhập từ khóa tìm kiếm vào ô tìm kiếm.
-Step 2: Người dùng nhấn nút "Tìm kiếm".
-Step 3: Kiểm tra thông báo "Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn.".</t>
+          <t>Step 1: Nhập từ khóa tìm kiếm vào ô tìm kiếm
+Step 2: Nhấn nút "Tìm kiếm"
+Step 3: Kiểm tra hệ thống không tìm thấy sản phẩm phù hợp
+Step 4: Kiểm tra thông báo "Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn." hiển thị</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>"Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn."</t>
+          <t>Không tìm thấy sản phẩm nào khớp với lựa chọn của bạn.</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="I7" s="11" t="n"/>
@@ -996,34 +989,34 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Kiểm tra gửi bình luận thành công khi nhập đầy đủ thông tin.</t>
+          <t>Kiểm tra gửi bình luận thành công khi nhập đầy đủ thông tin</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Hệ thống đang mở trang chi tiết sản phẩm.</t>
+          <t>Người dùng đang ở trang chủ website</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Truy cập vào trang chi tiết sản phẩm.
-Step 2: Nhập nội dung bình luận vào ô "Bình luận".
-Step 3: Nhập họ tên vào ô "Họ và tên".
-Step 4: Nhập số điện thoại hợp lệ vào ô "Số điện thoại".
-Step 5: Nhấn nút "Gửi bình luận".
-Step 6: Kiểm tra thông báo "Gửi bình luận thành công." hiển thị.</t>
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm
+Step 2: Nhập nội dung bình luận
+Step 3: Nhập họ tên
+Step 4: Nhập số điện thoại
+Step 5: Nhấn nút "Gửi bình luận"
+Step 6: Kiểm tra thông báo "Gửi bình luận thành công." hiển thị</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>"Gửi bình luận thành công." được hiển thị trên giao diện.</t>
+          <t>Gửi bình luận thành công.</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="I5" s="11" t="n"/>
@@ -1036,34 +1029,34 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Kiểm tra thông báo khi không nhập nội dung bình luận.</t>
+          <t>Kiểm tra lỗi khi nội dung bình luận rỗng</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Hệ thống đang mở trang chi tiết sản phẩm.</t>
+          <t>Người dùng đang ở trang chủ website</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Truy cập vào trang chi tiết sản phẩm.
-Step 2: Không nhập nội dung bình luận vào ô "Bình luận".
-Step 3: Nhập họ tên vào ô "Họ và tên".
-Step 4: Nhập số điện thoại hợp lệ vào ô "Số điện thoại".
-Step 5: Nhấn nút "Gửi bình luận".
-Step 6: Kiểm tra thông báo "Bạn chưa nhập bình luận." hiển thị.</t>
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm
+Step 2: Không nhập nội dung bình luận
+Step 3: Nhập họ tên
+Step 4: Nhập số điện thoại
+Step 5: Nhấn nút "Gửi bình luận"
+Step 6: Kiểm tra thông báo "Bạn chưa nhập bình luận." hiển thị</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>"Bạn chưa nhập bình luận." được hiển thị trên giao diện.</t>
+          <t>Bạn chưa nhập bình luận.</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="I6" s="11" t="n"/>
@@ -1076,34 +1069,34 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Kiểm tra thông báo khi không nhập họ tên.</t>
+          <t>Kiểm tra lỗi khi họ tên rỗng</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Hệ thống đang mở trang chi tiết sản phẩm.</t>
+          <t>Người dùng đang ở trang chủ website</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Truy cập vào trang chi tiết sản phẩm.
-Step 2: Nhập nội dung bình luận vào ô "Bình luận".
-Step 3: Không nhập họ tên vào ô "Họ và tên".
-Step 4: Nhập số điện thoại hợp lệ vào ô "Số điện thoại".
-Step 5: Nhấn nút "Gửi bình luận".
-Step 6: Kiểm tra thông báo "Bạn chưa nhập tên." hiển thị.</t>
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm
+Step 2: Nhập nội dung bình luận
+Step 3: Không nhập họ tên
+Step 4: Nhập số điện thoại
+Step 5: Nhấn nút "Gửi bình luận"
+Step 6: Kiểm tra thông báo "Bạn chưa nhập tên." hiển thị</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>"Bạn chưa nhập tên." được hiển thị trên giao diện.</t>
+          <t>Bạn chưa nhập tên.</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="I7" s="11" t="n"/>
@@ -1116,34 +1109,34 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Kiểm tra thông báo khi không nhập số điện thoại.</t>
+          <t>Kiểm tra lỗi khi số điện thoại rỗng</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Hệ thống đang mở trang chi tiết sản phẩm.</t>
+          <t>Người dùng đang ở trang chủ website</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Truy cập vào trang chi tiết sản phẩm.
-Step 2: Nhập nội dung bình luận vào ô "Bình luận".
-Step 3: Nhập họ tên vào ô "Họ và tên".
-Step 4: Không nhập số điện thoại vào ô "Số điện thoại".
-Step 5: Nhấn nút "Gửi bình luận".
-Step 6: Kiểm tra thông báo "Bạn chưa nhập số điện thoại." hiển thị.</t>
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm
+Step 2: Nhập nội dung bình luận
+Step 3: Nhập họ tên
+Step 4: Không nhập số điện thoại
+Step 5: Nhấn nút "Gửi bình luận"
+Step 6: Kiểm tra thông báo "Bạn chưa nhập số điện thoại." hiển thị</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>"Bạn chưa nhập số điện thoại." được hiển thị trên giao diện.</t>
+          <t>Bạn chưa nhập số điện thoại.</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="I8" s="11" t="n"/>
@@ -1156,34 +1149,34 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Kiểm tra thông báo khi nhập số điện thoại chứa ký tự không phải số.</t>
+          <t>Kiểm tra lỗi khi số điện thoại chứa ký tự không phải số</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Hệ thống đang mở trang chi tiết sản phẩm.</t>
+          <t>Người dùng đang ở trang chủ website</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Truy cập vào trang chi tiết sản phẩm.
-Step 2: Nhập nội dung bình luận vào ô "Bình luận".
-Step 3: Nhập họ tên vào ô "Họ và tên".
-Step 4: Nhập số điện thoại chứa ký tự không phải số vào ô "Số điện thoại".
-Step 5: Nhấn nút "Gửi bình luận".
-Step 6: Kiểm tra thông báo "Số điện thoại chỉ bao gồm những số." hiển thị.</t>
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm
+Step 2: Nhập nội dung bình luận
+Step 3: Nhập họ tên
+Step 4: Nhập số điện thoại chứa ký tự không phải số
+Step 5: Nhấn nút "Gửi bình luận"
+Step 6: Kiểm tra thông báo "Số điện thoại chỉ bao gồm những số." hiển thị</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>"Số điện thoại chỉ bao gồm những số." được hiển thị trên giao diện.</t>
+          <t>Số điện thoại chỉ bao gồm những số.</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="I9" s="11" t="n"/>
@@ -1196,34 +1189,34 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Kiểm tra thông báo khi nhập số điện thoại ít hơn 10 chữ số.</t>
+          <t>Kiểm tra lỗi khi số điện thoại ít hơn 10 chữ số</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Hệ thống đang mở trang chi tiết sản phẩm.</t>
+          <t>Người dùng đang ở trang chủ website</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Truy cập vào trang chi tiết sản phẩm.
-Step 2: Nhập nội dung bình luận vào ô "Bình luận".
-Step 3: Nhập họ tên vào ô "Họ và tên".
-Step 4: Nhập số điện thoại có ít hơn 10 chữ số vào ô "Số điện thoại".
-Step 5: Nhấn nút "Gửi bình luận".
-Step 6: Kiểm tra thông báo "Số điện thoại phải có ít nhất 10 số." hiển thị.</t>
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm
+Step 2: Nhập nội dung bình luận
+Step 3: Nhập họ tên
+Step 4: Nhập số điện thoại có ít hơn 10 chữ số
+Step 5: Nhấn nút "Gửi bình luận"
+Step 6: Kiểm tra thông báo "Số điện thoại phải có ít nhất 10 số." hiển thị</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>"Số điện thoại phải có ít nhất 10 số." được hiển thị trên giao diện.</t>
+          <t>Số điện thoại phải có ít nhất 10 số.</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="I10" s="11" t="n"/>
@@ -1395,19 +1388,19 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Kiểm tra đặt hàng nhanh khi nhập số điện thoại hợp lệ</t>
+          <t>Kiểm tra đặt hàng nhanh khi nhập số điện thoại hợp lệ và nhận thông báo thành công</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chi tiết sản phẩm</t>
+          <t>Người dùng đang ở trang chủ website</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Người dùng truy cập vào trang chi tiết sản phẩm
-Step 2: Người dùng nhập số điện thoại hợp lệ
-Step 3: Người dùng nhấn nút "Gửi"
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm
+Step 2: Nhập số điện thoại hợp lệ
+Step 3: Nhấn nút "Gửi"
 Step 4: Kiểm tra thông báo "Cảm ơn bạn đã đặt hàng, vui lòng check lại đơn hàng trong messenger." hiển thị</t>
         </is>
       </c>
@@ -1420,7 +1413,7 @@
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="I5" s="11" t="n"/>
@@ -1433,19 +1426,19 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Kiểm tra đặt hàng nhanh khi số điện thoại rỗng</t>
+          <t>Kiểm tra đặt hàng nhanh khi không nhập số điện thoại (số điện thoại rỗng)</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chi tiết sản phẩm</t>
+          <t>Người dùng đang ở trang chủ website</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Người dùng truy cập vào trang chi tiết sản phẩm
-Step 2: Người dùng không nhập số điện thoại
-Step 3: Người dùng nhấn nút "Gửi"
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm
+Step 2: Không nhập số điện thoại
+Step 3: Nhấn nút "Gửi"
 Step 4: Kiểm tra thông báo "Bạn chưa nhập số điện thoại." hiển thị</t>
         </is>
       </c>
@@ -1458,7 +1451,7 @@
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="I6" s="11" t="n"/>
@@ -1471,19 +1464,19 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Kiểm tra đặt hàng nhanh khi số điện thoại chứa ký tự không phải số</t>
+          <t>Kiểm tra đặt hàng nhanh khi nhập số điện thoại có ký tự không phải số</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chi tiết sản phẩm</t>
+          <t>Người dùng đang ở trang chủ website</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Người dùng truy cập vào trang chi tiết sản phẩm
-Step 2: Người dùng nhập số điện thoại chứa ký tự không phải số
-Step 3: Người dùng nhấn nút "Gửi"
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm
+Step 2: Nhập số điện thoại chứa ký tự không phải số
+Step 3: Nhấn nút "Gửi"
 Step 4: Kiểm tra thông báo "Số điện thoại chỉ bao gồm những số." hiển thị</t>
         </is>
       </c>
@@ -1496,7 +1489,7 @@
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="I7" s="11" t="n"/>
@@ -1509,19 +1502,19 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Kiểm tra đặt hàng nhanh khi số điện thoại ít hơn 10 chữ số</t>
+          <t>Kiểm tra đặt hàng nhanh khi nhập số điện thoại ít hơn 10 chữ số</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chi tiết sản phẩm</t>
+          <t>Người dùng đang ở trang chủ website</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Step 1: Người dùng truy cập vào trang chi tiết sản phẩm
-Step 2: Người dùng nhập số điện thoại có ít hơn 10 chữ số
-Step 3: Người dùng nhấn nút "Gửi"
+          <t>Step 1: Truy cập vào trang chi tiết sản phẩm
+Step 2: Nhập số điện thoại có ít hơn 10 chữ số
+Step 3: Nhấn nút "Gửi"
 Step 4: Kiểm tra thông báo "Số điện thoại phải có ít nhất 10 số." hiển thị</t>
         </is>
       </c>
@@ -1534,7 +1527,7 @@
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="I8" s="11" t="n"/>
@@ -1708,12 +1701,12 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Mua hàng thành công khi tất cả thông tin hợp lệ</t>
+          <t>Kiểm tra đặt hàng nhanh thành công khi nhập đầy đủ thông tin</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Người dùng đang ở trang chủ website</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -1725,25 +1718,24 @@
 Step 5: Nhập địa chỉ nhận hàng
 Step 6: Nhập yêu cầu thêm (nếu có)
 Step 7: Nhấn nút "Mua"
-Step 8: Kiểm tra dữ liệu nhập</t>
+Step 8: Kiểm tra thông báo "Cảm ơn bạn đã đặt hàng, vui lòng check lại đơn hàng trong messenger." hiển thị</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Hệ thống gửi thông tin đơn hàng
-Hiển thị thông báo chứa “Cảm ơn bạn đã đặt hàng, vui lòng check lại đơn hàng trong messenger.”</t>
+          <t>Cảm ơn bạn đã đặt hàng, vui lòng check lại đơn hàng trong messenger.</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="I5" s="11" t="n"/>
     </row>
-    <row r="6" ht="90" customHeight="1">
+    <row r="6" ht="120" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>TC_002</t>
@@ -1751,12 +1743,12 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Không nhập họ và tên người mua</t>
+          <t>Kiểm tra thông báo khi họ và tên người mua rỗng</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Người dùng đang ở trang chủ website</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1766,24 +1758,26 @@
 Step 3: Không nhập họ và tên người mua
 Step 4: Nhập số điện thoại
 Step 5: Nhập địa chỉ nhận hàng
-Step 6: Nhấn nút "Mua"</t>
+Step 6: Nhập yêu cầu thêm (nếu có)
+Step 7: Nhấn nút "Mua"
+Step 8: Kiểm tra thông báo "Bạn chưa nhập họ và tên người mua." hiển thị</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo "Bạn chưa nhập họ và tên người mua."</t>
+          <t>Bạn chưa nhập họ và tên người mua.</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="I6" s="11" t="n"/>
     </row>
-    <row r="7" ht="90" customHeight="1">
+    <row r="7" ht="120" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>TC_003</t>
@@ -1791,12 +1785,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Không nhập số điện thoại</t>
+          <t>Kiểm tra thông báo khi số điện thoại rỗng</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Người dùng đang ở trang chủ website</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -1806,24 +1800,26 @@
 Step 3: Nhập họ và tên người mua
 Step 4: Không nhập số điện thoại
 Step 5: Nhập địa chỉ nhận hàng
-Step 6: Nhấn nút "Mua"</t>
+Step 6: Nhập yêu cầu thêm (nếu có)
+Step 7: Nhấn nút "Mua"
+Step 8: Kiểm tra thông báo "Bạn chưa nhập số điện thoại người mua." hiển thị</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo "Bạn chưa nhập số điện thoại."</t>
+          <t>Bạn chưa nhập số điện thoại người mua.</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="I7" s="11" t="n"/>
     </row>
-    <row r="8" ht="90" customHeight="1">
+    <row r="8" ht="120" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
           <t>TC_004</t>
@@ -1831,12 +1827,12 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Số điện thoại chứa ký tự không phải số</t>
+          <t>Kiểm tra thông báo khi số điện thoại chứa ký tự không phải số</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Người dùng đang ở trang chủ website</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -1846,24 +1842,26 @@
 Step 3: Nhập họ và tên người mua
 Step 4: Nhập số điện thoại chứa ký tự không phải số
 Step 5: Nhập địa chỉ nhận hàng
-Step 6: Nhấn nút "Mua"</t>
+Step 6: Nhập yêu cầu thêm (nếu có)
+Step 7: Nhấn nút "Mua"
+Step 8: Kiểm tra thông báo "Số điện thoại chỉ bao gồm những số." hiển thị</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo "Số điện thoại chỉ bao gồm những số."</t>
+          <t>Số điện thoại chỉ bao gồm những số.</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="I8" s="11" t="n"/>
     </row>
-    <row r="9" ht="90" customHeight="1">
+    <row r="9" ht="120" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
           <t>TC_005</t>
@@ -1871,12 +1869,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Số điện thoại ít hơn 10 chữ số</t>
+          <t>Kiểm tra thông báo khi số điện thoại ít hơn 10 chữ số</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Người dùng đang ở trang chủ website</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -1886,24 +1884,26 @@
 Step 3: Nhập họ và tên người mua
 Step 4: Nhập số điện thoại có ít hơn 10 chữ số
 Step 5: Nhập địa chỉ nhận hàng
-Step 6: Nhấn nút "Mua"</t>
+Step 6: Nhập yêu cầu thêm (nếu có)
+Step 7: Nhấn nút "Mua"
+Step 8: Kiểm tra thông báo "Số điện thoại phải có ít nhất 10 số." hiển thị</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo "Số điện thoại phải có ít nhất 10 số."</t>
+          <t>Số điện thoại phải có ít nhất 10 số.</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="I9" s="11" t="n"/>
     </row>
-    <row r="10" ht="90" customHeight="1">
+    <row r="10" ht="120" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
           <t>TC_006</t>
@@ -1911,12 +1911,12 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Không nhập địa chỉ nhận hàng</t>
+          <t>Kiểm tra thông báo khi địa chỉ nhận hàng rỗng</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Người dùng đang ở trang chủ</t>
+          <t>Người dùng đang ở trang chủ website</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -1926,19 +1926,21 @@
 Step 3: Nhập họ và tên người mua
 Step 4: Nhập số điện thoại
 Step 5: Không nhập địa chỉ nhận hàng
-Step 6: Nhấn nút "Mua"</t>
+Step 6: Nhập yêu cầu thêm (nếu có)
+Step 7: Nhấn nút "Mua"
+Step 8: Kiểm tra thông báo "Bạn chưa nhập địa chỉ nhận hàng." hiển thị</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo "Bạn chưa nhập địa chỉ nhận hàng."</t>
+          <t>Bạn chưa nhập địa chỉ nhận hàng.</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="I10" s="11" t="n"/>
